--- a/artfynd/A 15170-2024 artfynd.xlsx
+++ b/artfynd/A 15170-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121171421</v>
+        <v>121171425</v>
       </c>
       <c r="B2" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547834</v>
+        <v>547866</v>
       </c>
       <c r="R2" t="n">
-        <v>6346444</v>
+        <v>6346431</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171425</v>
+        <v>121171420</v>
       </c>
       <c r="B3" t="n">
-        <v>100337</v>
+        <v>101250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547866</v>
+        <v>547838</v>
       </c>
       <c r="R3" t="n">
-        <v>6346431</v>
+        <v>6346446</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171428</v>
+        <v>121171421</v>
       </c>
       <c r="B4" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547907</v>
+        <v>547834</v>
       </c>
       <c r="R4" t="n">
-        <v>6346437</v>
+        <v>6346444</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171423</v>
+        <v>121171428</v>
       </c>
       <c r="B5" t="n">
-        <v>74517</v>
+        <v>100347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547838</v>
+        <v>547907</v>
       </c>
       <c r="R5" t="n">
-        <v>6346433</v>
+        <v>6346437</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,11 +1078,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171420</v>
+        <v>121171423</v>
       </c>
       <c r="B6" t="n">
-        <v>101240</v>
+        <v>74520</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,33 +1124,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>6428</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
@@ -1156,7 +1151,7 @@
         <v>547838</v>
       </c>
       <c r="R6" t="n">
-        <v>6346446</v>
+        <v>6346433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,6 +1184,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 15170-2024 artfynd.xlsx
+++ b/artfynd/A 15170-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171420</v>
+        <v>121171423</v>
       </c>
       <c r="B3" t="n">
-        <v>101250</v>
+        <v>74520</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,33 +797,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
@@ -833,7 +824,7 @@
         <v>547838</v>
       </c>
       <c r="R3" t="n">
-        <v>6346446</v>
+        <v>6346433</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171421</v>
+        <v>121171420</v>
       </c>
       <c r="B4" t="n">
-        <v>100347</v>
+        <v>101250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,34 +908,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547834</v>
+        <v>547838</v>
       </c>
       <c r="R4" t="n">
-        <v>6346444</v>
+        <v>6346446</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1108,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171423</v>
+        <v>121171421</v>
       </c>
       <c r="B6" t="n">
-        <v>74520</v>
+        <v>100347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6428</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547838</v>
+        <v>547834</v>
       </c>
       <c r="R6" t="n">
-        <v>6346433</v>
+        <v>6346444</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,11 +1189,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 15170-2024 artfynd.xlsx
+++ b/artfynd/A 15170-2024 artfynd.xlsx
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171428</v>
+        <v>121171421</v>
       </c>
       <c r="B5" t="n">
         <v>100347</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547907</v>
+        <v>547834</v>
       </c>
       <c r="R5" t="n">
-        <v>6346437</v>
+        <v>6346444</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171421</v>
+        <v>121171428</v>
       </c>
       <c r="B6" t="n">
         <v>100347</v>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547834</v>
+        <v>547907</v>
       </c>
       <c r="R6" t="n">
-        <v>6346444</v>
+        <v>6346437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 15170-2024 artfynd.xlsx
+++ b/artfynd/A 15170-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121171425</v>
       </c>
       <c r="B2" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171423</v>
+        <v>121171420</v>
       </c>
       <c r="B3" t="n">
-        <v>74520</v>
+        <v>101263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,24 +797,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
@@ -824,7 +833,7 @@
         <v>547838</v>
       </c>
       <c r="R3" t="n">
-        <v>6346433</v>
+        <v>6346446</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,11 +866,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171420</v>
+        <v>121171428</v>
       </c>
       <c r="B4" t="n">
-        <v>101250</v>
+        <v>100360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,43 +912,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547838</v>
+        <v>547907</v>
       </c>
       <c r="R4" t="n">
-        <v>6346446</v>
+        <v>6346437</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171421</v>
+        <v>121171423</v>
       </c>
       <c r="B5" t="n">
-        <v>100347</v>
+        <v>74522</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547834</v>
+        <v>547838</v>
       </c>
       <c r="R5" t="n">
-        <v>6346444</v>
+        <v>6346433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,6 +1078,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171428</v>
+        <v>121171421</v>
       </c>
       <c r="B6" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547907</v>
+        <v>547834</v>
       </c>
       <c r="R6" t="n">
-        <v>6346437</v>
+        <v>6346444</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 15170-2024 artfynd.xlsx
+++ b/artfynd/A 15170-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121171425</v>
+        <v>121171428</v>
       </c>
       <c r="B2" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547866</v>
+        <v>547907</v>
       </c>
       <c r="R2" t="n">
-        <v>6346431</v>
+        <v>6346437</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171420</v>
+        <v>121171421</v>
       </c>
       <c r="B3" t="n">
-        <v>101263</v>
+        <v>100361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,43 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547838</v>
+        <v>547834</v>
       </c>
       <c r="R3" t="n">
-        <v>6346446</v>
+        <v>6346444</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171428</v>
+        <v>121171423</v>
       </c>
       <c r="B4" t="n">
-        <v>100360</v>
+        <v>74522</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547907</v>
+        <v>547838</v>
       </c>
       <c r="R4" t="n">
-        <v>6346437</v>
+        <v>6346433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171423</v>
+        <v>121171420</v>
       </c>
       <c r="B5" t="n">
-        <v>74522</v>
+        <v>101264</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,24 +1014,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
@@ -1045,7 +1050,7 @@
         <v>547838</v>
       </c>
       <c r="R5" t="n">
-        <v>6346433</v>
+        <v>6346446</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,11 +1083,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171421</v>
+        <v>121171425</v>
       </c>
       <c r="B6" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547834</v>
+        <v>547866</v>
       </c>
       <c r="R6" t="n">
-        <v>6346444</v>
+        <v>6346431</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 15170-2024 artfynd.xlsx
+++ b/artfynd/A 15170-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121171428</v>
+        <v>121171423</v>
       </c>
       <c r="B2" t="n">
-        <v>100361</v>
+        <v>74525</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547907</v>
+        <v>547838</v>
       </c>
       <c r="R2" t="n">
-        <v>6346437</v>
+        <v>6346433</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171421</v>
+        <v>121171425</v>
       </c>
       <c r="B3" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547834</v>
+        <v>547866</v>
       </c>
       <c r="R3" t="n">
-        <v>6346444</v>
+        <v>6346431</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171423</v>
+        <v>121171428</v>
       </c>
       <c r="B4" t="n">
-        <v>74522</v>
+        <v>100364</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547838</v>
+        <v>547907</v>
       </c>
       <c r="R4" t="n">
-        <v>6346433</v>
+        <v>6346437</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171420</v>
+        <v>121171421</v>
       </c>
       <c r="B5" t="n">
-        <v>101264</v>
+        <v>100364</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,43 +1014,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547838</v>
+        <v>547834</v>
       </c>
       <c r="R5" t="n">
-        <v>6346446</v>
+        <v>6346444</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171425</v>
+        <v>121171420</v>
       </c>
       <c r="B6" t="n">
-        <v>100361</v>
+        <v>101267</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,34 +1120,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547866</v>
+        <v>547838</v>
       </c>
       <c r="R6" t="n">
-        <v>6346431</v>
+        <v>6346446</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 15170-2024 artfynd.xlsx
+++ b/artfynd/A 15170-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121171423</v>
+        <v>121171428</v>
       </c>
       <c r="B2" t="n">
-        <v>74525</v>
+        <v>100364</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547838</v>
+        <v>547907</v>
       </c>
       <c r="R2" t="n">
-        <v>6346433</v>
+        <v>6346437</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -892,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171428</v>
+        <v>121171421</v>
       </c>
       <c r="B4" t="n">
         <v>100364</v>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547907</v>
+        <v>547834</v>
       </c>
       <c r="R4" t="n">
-        <v>6346437</v>
+        <v>6346444</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171421</v>
+        <v>121171420</v>
       </c>
       <c r="B5" t="n">
-        <v>100364</v>
+        <v>101267</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,34 +1009,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547834</v>
+        <v>547838</v>
       </c>
       <c r="R5" t="n">
-        <v>6346444</v>
+        <v>6346446</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171420</v>
+        <v>121171423</v>
       </c>
       <c r="B6" t="n">
-        <v>101267</v>
+        <v>74525</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,33 +1124,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>6428</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
@@ -1156,7 +1151,7 @@
         <v>547838</v>
       </c>
       <c r="R6" t="n">
-        <v>6346446</v>
+        <v>6346433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,6 +1184,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 15170-2024 artfynd.xlsx
+++ b/artfynd/A 15170-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171420</v>
+        <v>121171423</v>
       </c>
       <c r="B5" t="n">
-        <v>101267</v>
+        <v>74525</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,33 +1009,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>6428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
@@ -1045,7 +1036,7 @@
         <v>547838</v>
       </c>
       <c r="R5" t="n">
-        <v>6346446</v>
+        <v>6346433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171423</v>
+        <v>121171420</v>
       </c>
       <c r="B6" t="n">
-        <v>74525</v>
+        <v>101267</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,24 +1120,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6428</v>
+        <v>221235</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
@@ -1151,7 +1156,7 @@
         <v>547838</v>
       </c>
       <c r="R6" t="n">
-        <v>6346433</v>
+        <v>6346446</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,11 +1189,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 15170-2024 artfynd.xlsx
+++ b/artfynd/A 15170-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121171428</v>
+        <v>121171421</v>
       </c>
       <c r="B2" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547907</v>
+        <v>547834</v>
       </c>
       <c r="R2" t="n">
-        <v>6346437</v>
+        <v>6346444</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171425</v>
+        <v>121171420</v>
       </c>
       <c r="B3" t="n">
-        <v>100364</v>
+        <v>101273</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547866</v>
+        <v>547838</v>
       </c>
       <c r="R3" t="n">
-        <v>6346431</v>
+        <v>6346446</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171421</v>
+        <v>121171423</v>
       </c>
       <c r="B4" t="n">
-        <v>100364</v>
+        <v>74526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547834</v>
+        <v>547838</v>
       </c>
       <c r="R4" t="n">
-        <v>6346444</v>
+        <v>6346433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +972,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171423</v>
+        <v>121171428</v>
       </c>
       <c r="B5" t="n">
-        <v>74525</v>
+        <v>100370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547838</v>
+        <v>547907</v>
       </c>
       <c r="R5" t="n">
-        <v>6346433</v>
+        <v>6346437</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,11 +1083,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171420</v>
+        <v>121171425</v>
       </c>
       <c r="B6" t="n">
-        <v>101267</v>
+        <v>100370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,43 +1129,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547838</v>
+        <v>547866</v>
       </c>
       <c r="R6" t="n">
-        <v>6346446</v>
+        <v>6346431</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 15170-2024 artfynd.xlsx
+++ b/artfynd/A 15170-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121171421</v>
+        <v>121171431</v>
       </c>
       <c r="B2" t="n">
-        <v>100370</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547834</v>
+        <v>547968</v>
       </c>
       <c r="R2" t="n">
-        <v>6346444</v>
+        <v>6346368</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171420</v>
+        <v>121171423</v>
       </c>
       <c r="B3" t="n">
-        <v>101273</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,33 +792,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
@@ -833,7 +819,7 @@
         <v>547838</v>
       </c>
       <c r="R3" t="n">
-        <v>6346446</v>
+        <v>6346433</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +852,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171423</v>
+        <v>121171419</v>
       </c>
       <c r="B4" t="n">
-        <v>74526</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,37 +898,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>100038</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547838</v>
+        <v>547805</v>
       </c>
       <c r="R4" t="n">
-        <v>6346433</v>
+        <v>6346447</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171428</v>
+        <v>121171266</v>
       </c>
       <c r="B5" t="n">
-        <v>100370</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,34 +1004,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547907</v>
+        <v>547975</v>
       </c>
       <c r="R5" t="n">
-        <v>6346437</v>
+        <v>6346474</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,50 +1099,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171425</v>
+        <v>121171265</v>
       </c>
       <c r="B6" t="n">
-        <v>100370</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547866</v>
+        <v>547980</v>
       </c>
       <c r="R6" t="n">
-        <v>6346431</v>
+        <v>6346387</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,12 +1173,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,6 +1202,525 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121171420</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gällingsbotrakten, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>547838</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6346446</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mörlunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121171416</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gällingsbotrakten, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>547804</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6346453</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mörlunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Välspridd</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121171421</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gällingsbotrakten, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>547834</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6346444</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mörlunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121171425</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gällingsbotrakten, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>547866</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6346431</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mörlunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121171428</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gällingsbotrakten, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>547907</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6346437</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mörlunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 15170-2024 artfynd.xlsx
+++ b/artfynd/A 15170-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171431</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171423</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171419</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171266</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171265</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1316,6 +1346,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171420</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1422,6 +1457,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171416</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171421</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1624,6 +1669,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171425</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1725,8 +1775,25 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121171428</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>